--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SOL GIRONÈS BISBAL BÀSQUET.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SOL GIRONÈS BISBAL BÀSQUET.xlsx
@@ -565,13 +565,13 @@
         <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>59.2435</v>
+        <v>31.6262</v>
       </c>
       <c r="E2" t="n">
-        <v>29.5142</v>
+        <v>14.1379</v>
       </c>
       <c r="F2" t="n">
-        <v>29.729</v>
+        <v>17.4884</v>
       </c>
       <c r="G2" t="n">
         <v>3.5049</v>
@@ -610,13 +610,13 @@
         <v>59.1385</v>
       </c>
       <c r="S2" t="n">
-        <v>45.0135</v>
+        <v>17.3961</v>
       </c>
       <c r="T2" t="n">
-        <v>18.6911</v>
+        <v>3.3144</v>
       </c>
       <c r="U2" t="n">
-        <v>26.3225</v>
+        <v>14.0821</v>
       </c>
       <c r="V2" t="n">
         <v>18.9387</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. DOMINGUEZ ESPELT</t>
+          <t>B. ALVAREZ TORRES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>12.3358</v>
+        <v>23.6298</v>
       </c>
       <c r="E3" t="n">
-        <v>11.8505</v>
+        <v>23.2065</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4851999999999997</v>
+        <v>0.4229000000000003</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2194</v>
+        <v>16.2931</v>
       </c>
       <c r="H3" t="n">
-        <v>6.9499</v>
+        <v>-13.7165</v>
       </c>
       <c r="I3" t="n">
-        <v>-5.7307</v>
+        <v>30.0098</v>
       </c>
       <c r="J3" t="n">
-        <v>12.0809</v>
+        <v>61.0526</v>
       </c>
       <c r="K3" t="n">
-        <v>13.3727</v>
+        <v>13.1365</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.2918</v>
+        <v>47.9162</v>
       </c>
       <c r="M3" t="n">
-        <v>-10.8615</v>
+        <v>-44.7594</v>
       </c>
       <c r="N3" t="n">
-        <v>-6.422800000000001</v>
+        <v>-26.853</v>
       </c>
       <c r="O3" t="n">
-        <v>-4.438800000000001</v>
+        <v>-17.9062</v>
       </c>
       <c r="P3" t="n">
-        <v>4.3121</v>
+        <v>2.2588</v>
       </c>
       <c r="Q3" t="n">
-        <v>-9.445600000000001</v>
+        <v>-54.8263</v>
       </c>
       <c r="R3" t="n">
-        <v>13.7579</v>
+        <v>57.0849</v>
       </c>
       <c r="S3" t="n">
-        <v>-5.7381</v>
+        <v>-6.7087</v>
       </c>
       <c r="T3" t="n">
-        <v>-2.9651</v>
+        <v>-6.5059</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.7731</v>
+        <v>-0.2028999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>12.5423</v>
+        <v>11.7862</v>
       </c>
       <c r="W3" t="n">
-        <v>12.1805</v>
+        <v>23.4862</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3618</v>
+        <v>-11.6997</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>11.3762</v>
+        <v>18.1841</v>
       </c>
       <c r="E4" t="n">
-        <v>-5.681899999999999</v>
+        <v>1.780000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>17.0578</v>
+        <v>16.4037</v>
       </c>
       <c r="G4" t="n">
         <v>-1.9195</v>
@@ -766,13 +766,13 @@
         <v>41.8897</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5553999999999998</v>
+        <v>6.2525</v>
       </c>
       <c r="T4" t="n">
-        <v>-9.7628</v>
+        <v>-2.3008</v>
       </c>
       <c r="U4" t="n">
-        <v>9.2074</v>
+        <v>8.5532</v>
       </c>
       <c r="V4" t="n">
         <v>7.074999999999999</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. ALVAREZ TORRES</t>
+          <t>A. DOMINGUEZ ESPELT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2019</v>
+        <v>17.4461</v>
       </c>
       <c r="E5" t="n">
-        <v>6.810899999999998</v>
+        <v>14.3105</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.609</v>
+        <v>3.1356</v>
       </c>
       <c r="G5" t="n">
-        <v>16.2931</v>
+        <v>1.2194</v>
       </c>
       <c r="H5" t="n">
-        <v>-13.7165</v>
+        <v>6.9499</v>
       </c>
       <c r="I5" t="n">
-        <v>30.0098</v>
+        <v>-5.7307</v>
       </c>
       <c r="J5" t="n">
-        <v>61.0526</v>
+        <v>12.0809</v>
       </c>
       <c r="K5" t="n">
-        <v>13.1365</v>
+        <v>13.3727</v>
       </c>
       <c r="L5" t="n">
-        <v>47.9162</v>
+        <v>-1.2918</v>
       </c>
       <c r="M5" t="n">
-        <v>-44.7594</v>
+        <v>-10.8615</v>
       </c>
       <c r="N5" t="n">
-        <v>-26.853</v>
+        <v>-6.422800000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-17.9062</v>
+        <v>-4.438800000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2588</v>
+        <v>4.3121</v>
       </c>
       <c r="Q5" t="n">
-        <v>-54.8263</v>
+        <v>-9.445600000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>57.0849</v>
+        <v>13.7579</v>
       </c>
       <c r="S5" t="n">
-        <v>-28.1367</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-22.902</v>
+        <v>-0.5050000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-5.2346</v>
+        <v>-0.1229</v>
       </c>
       <c r="V5" t="n">
-        <v>11.7862</v>
+        <v>12.5423</v>
       </c>
       <c r="W5" t="n">
-        <v>23.4862</v>
+        <v>12.1805</v>
       </c>
       <c r="X5" t="n">
-        <v>-11.6997</v>
+        <v>0.3618</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4731</v>
+        <v>1.5027</v>
       </c>
       <c r="E6" t="n">
         <v>0.9031</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5699</v>
+        <v>0.5996</v>
       </c>
       <c r="G6" t="n">
         <v>0.4184</v>
@@ -922,13 +922,13 @@
         <v>0.2053</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0198</v>
+        <v>0.0494</v>
       </c>
       <c r="T6" t="n">
         <v>0.0736</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0538</v>
+        <v>-0.0242</v>
       </c>
       <c r="V6" t="n">
         <v>0.8295</v>
@@ -955,13 +955,13 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7542000000000001</v>
+        <v>0.9386</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6595</v>
+        <v>-0.5935999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4138</v>
+        <v>1.5324</v>
       </c>
       <c r="G7" t="n">
         <v>1.3494</v>
@@ -1000,13 +1000,13 @@
         <v>0.616</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1844</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2557</v>
+        <v>-0.1898</v>
       </c>
       <c r="U7" t="n">
-        <v>0.07139999999999999</v>
+        <v>0.1899</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4682</v>
+        <v>0.6913</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0062</v>
+        <v>0.0984</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4743</v>
+        <v>0.5929</v>
       </c>
       <c r="G8" t="n">
         <v>0.3155</v>
@@ -1078,13 +1078,13 @@
         <v>0.4107</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.258</v>
+        <v>-0.0349</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.124</v>
+        <v>-0.0194</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.134</v>
+        <v>-0.0155</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. VILA I GÓMEZ</t>
+          <t>J. GOLSON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.483699999999999</v>
+        <v>-0.5175000000000005</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8227</v>
+        <v>5.3828</v>
       </c>
       <c r="F9" t="n">
-        <v>1.339</v>
+        <v>-5.900099999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.023999999999999</v>
+        <v>-4.6853</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.5694</v>
+        <v>-4.2807</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4548</v>
+        <v>-0.4043000000000005</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6636999999999997</v>
+        <v>7.1555</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.05720000000000003</v>
+        <v>2.7001</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6067</v>
+        <v>4.455400000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.3602</v>
+        <v>-11.8407</v>
       </c>
       <c r="N9" t="n">
-        <v>-3.5121</v>
+        <v>-6.9806</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8484999999999999</v>
+        <v>-4.86</v>
       </c>
       <c r="P9" t="n">
-        <v>2.4641</v>
+        <v>2.2588</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.9281</v>
+        <v>-9.035</v>
       </c>
       <c r="R9" t="n">
-        <v>7.3922</v>
+        <v>11.2938</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3392</v>
+        <v>-3.277</v>
       </c>
       <c r="T9" t="n">
-        <v>2.0486</v>
+        <v>-2.8875</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7094</v>
+        <v>-0.3894</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2627999999999999</v>
+        <v>5.1858</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7206999999999999</v>
+        <v>10.1495</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.9834000000000001</v>
+        <v>-4.9637</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. LAROUSSE</t>
+          <t>A. VILA I GÓMEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5855</v>
+        <v>-2.8006</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9621</v>
+        <v>-4.783099999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3763999999999998</v>
+        <v>1.9825</v>
       </c>
       <c r="G10" t="n">
-        <v>-11.6096</v>
+        <v>-5.023999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-5.1663</v>
+        <v>-3.5694</v>
       </c>
       <c r="I10" t="n">
-        <v>-6.4433</v>
+        <v>-1.4548</v>
       </c>
       <c r="J10" t="n">
-        <v>5.597899999999999</v>
+        <v>-0.6636999999999997</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9411</v>
+        <v>-0.05720000000000003</v>
       </c>
       <c r="L10" t="n">
-        <v>2.6568</v>
+        <v>-0.6067</v>
       </c>
       <c r="M10" t="n">
-        <v>-17.2077</v>
+        <v>-4.3602</v>
       </c>
       <c r="N10" t="n">
-        <v>-8.1075</v>
+        <v>-3.5121</v>
       </c>
       <c r="O10" t="n">
-        <v>-9.100300000000001</v>
+        <v>-0.8484999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2054999999999998</v>
+        <v>2.4641</v>
       </c>
       <c r="Q10" t="n">
-        <v>-19.9181</v>
+        <v>-4.9281</v>
       </c>
       <c r="R10" t="n">
-        <v>20.1236</v>
+        <v>7.3922</v>
       </c>
       <c r="S10" t="n">
-        <v>14.4403</v>
+        <v>0.02229999999999993</v>
       </c>
       <c r="T10" t="n">
-        <v>11.7484</v>
+        <v>0.08829999999999993</v>
       </c>
       <c r="U10" t="n">
-        <v>2.6918</v>
+        <v>-0.06620000000000004</v>
       </c>
       <c r="V10" t="n">
-        <v>-5.6214</v>
+        <v>-0.2627999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3904000000000001</v>
+        <v>0.7206999999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>-5.231100000000001</v>
+        <v>-0.9834000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. KANE</t>
+          <t>D. EFAMBE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.664199999999999</v>
+        <v>-6.4068</v>
       </c>
       <c r="E11" t="n">
-        <v>-15.3537</v>
+        <v>-4.2902</v>
       </c>
       <c r="F11" t="n">
-        <v>10.6898</v>
+        <v>-2.1166</v>
       </c>
       <c r="G11" t="n">
-        <v>-14.4035</v>
+        <v>-5.36</v>
       </c>
       <c r="H11" t="n">
-        <v>-13.7548</v>
+        <v>-3.4607</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6485000000000001</v>
+        <v>-1.8994</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.511200000000001</v>
+        <v>-2.4272</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.221</v>
+        <v>-2.5456</v>
       </c>
       <c r="L11" t="n">
-        <v>3.7101</v>
+        <v>0.1184</v>
       </c>
       <c r="M11" t="n">
-        <v>-12.8923</v>
+        <v>-2.9329</v>
       </c>
       <c r="N11" t="n">
-        <v>-8.533999999999999</v>
+        <v>-0.9151</v>
       </c>
       <c r="O11" t="n">
-        <v>-4.3582</v>
+        <v>-2.0178</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6161000000000003</v>
+        <v>-2.2588</v>
       </c>
       <c r="Q11" t="n">
-        <v>-25.4623</v>
+        <v>-4.1068</v>
       </c>
       <c r="R11" t="n">
-        <v>24.8462</v>
+        <v>1.8481</v>
       </c>
       <c r="S11" t="n">
-        <v>19.2903</v>
+        <v>0.863</v>
       </c>
       <c r="T11" t="n">
-        <v>13.7779</v>
+        <v>1.0652</v>
       </c>
       <c r="U11" t="n">
-        <v>5.5126</v>
+        <v>-0.2022</v>
       </c>
       <c r="V11" t="n">
-        <v>-8.9352</v>
+        <v>0.3491</v>
       </c>
       <c r="W11" t="n">
-        <v>-2.1584</v>
+        <v>1.1786</v>
       </c>
       <c r="X11" t="n">
-        <v>-6.776800000000001</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. EFAMBE</t>
+          <t>P. SALA VALLMAJO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8426</v>
+        <v>-7.3483</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5778</v>
+        <v>-2.5872</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.2648</v>
+        <v>-4.761100000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.36</v>
+        <v>-4.131499999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.4607</v>
+        <v>-0.2301999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.8994</v>
+        <v>-3.9015</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.4272</v>
+        <v>10.9276</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.5456</v>
+        <v>9.2599</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1184</v>
+        <v>1.6673</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.9329</v>
+        <v>-15.0591</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9151</v>
+        <v>-9.4902</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.0178</v>
+        <v>-5.5691</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.2588</v>
+        <v>8.0085</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.1068</v>
+        <v>-12.9365</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8481</v>
+        <v>20.9449</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4272</v>
+        <v>-5.680899999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>2.7776</v>
+        <v>-1.9969</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3505</v>
+        <v>-3.6838</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3491</v>
+        <v>-5.544</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1786</v>
+        <v>1.4188</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.8295</v>
+        <v>-6.962899999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. GOLSON</t>
+          <t>C. LAROUSSE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.8736</v>
+        <v>-10.2722</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4309</v>
+        <v>-11.1559</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.304500000000001</v>
+        <v>0.8837000000000002</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.6853</v>
+        <v>-11.6096</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.2807</v>
+        <v>-5.1663</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4043000000000005</v>
+        <v>-6.4433</v>
       </c>
       <c r="J13" t="n">
-        <v>7.1555</v>
+        <v>5.597899999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>2.7001</v>
+        <v>2.9411</v>
       </c>
       <c r="L13" t="n">
-        <v>4.455400000000001</v>
+        <v>2.6568</v>
       </c>
       <c r="M13" t="n">
-        <v>-11.8407</v>
+        <v>-17.2077</v>
       </c>
       <c r="N13" t="n">
-        <v>-6.9806</v>
+        <v>-8.1075</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.86</v>
+        <v>-9.100300000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2588</v>
+        <v>0.2054999999999998</v>
       </c>
       <c r="Q13" t="n">
-        <v>-9.035</v>
+        <v>-19.9181</v>
       </c>
       <c r="R13" t="n">
-        <v>11.2938</v>
+        <v>20.1236</v>
       </c>
       <c r="S13" t="n">
-        <v>-9.632999999999999</v>
+        <v>6.7537</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.8393</v>
+        <v>3.5547</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.7938</v>
+        <v>3.1991</v>
       </c>
       <c r="V13" t="n">
-        <v>5.1858</v>
+        <v>-5.6214</v>
       </c>
       <c r="W13" t="n">
-        <v>10.1495</v>
+        <v>-0.3904000000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.9637</v>
+        <v>-5.231100000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>-7.327800000000001</v>
+        <v>-10.8952</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.6401</v>
+        <v>-12.7672</v>
       </c>
       <c r="F14" t="n">
-        <v>3.3126</v>
+        <v>1.872300000000001</v>
       </c>
       <c r="G14" t="n">
         <v>-15.9031</v>
@@ -1546,13 +1546,13 @@
         <v>18.8916</v>
       </c>
       <c r="S14" t="n">
-        <v>4.208</v>
+        <v>0.6410999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2763999999999999</v>
+        <v>-1.8503</v>
       </c>
       <c r="U14" t="n">
-        <v>3.9315</v>
+        <v>2.4913</v>
       </c>
       <c r="V14" t="n">
         <v>0.671</v>
@@ -1579,13 +1579,13 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>-13.0036</v>
+        <v>-11.1575</v>
       </c>
       <c r="E15" t="n">
-        <v>-13.0446</v>
+        <v>-12.0876</v>
       </c>
       <c r="F15" t="n">
-        <v>0.04099999999999993</v>
+        <v>0.9303000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>-11.5573</v>
@@ -1624,13 +1624,13 @@
         <v>13.1419</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.1311</v>
+        <v>-0.2847999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.682</v>
+        <v>-1.7251</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5509000000000002</v>
+        <v>1.4401</v>
       </c>
       <c r="V15" t="n">
         <v>-3.2169</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. SALA VALLMAJO</t>
+          <t>X. TORRENT BAYÉ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>-13.8412</v>
+        <v>-16.7235</v>
       </c>
       <c r="E16" t="n">
-        <v>-5.4656</v>
+        <v>-23.6492</v>
       </c>
       <c r="F16" t="n">
-        <v>-8.375400000000001</v>
+        <v>6.9258</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.131499999999999</v>
+        <v>-40.5118</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2301999999999999</v>
+        <v>-7.8356</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.9015</v>
+        <v>-32.6763</v>
       </c>
       <c r="J16" t="n">
-        <v>10.9276</v>
+        <v>-8.125299999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>9.2599</v>
+        <v>11.4898</v>
       </c>
       <c r="L16" t="n">
-        <v>1.6673</v>
+        <v>-19.6153</v>
       </c>
       <c r="M16" t="n">
-        <v>-15.0591</v>
+        <v>-32.3863</v>
       </c>
       <c r="N16" t="n">
-        <v>-9.4902</v>
+        <v>-19.3255</v>
       </c>
       <c r="O16" t="n">
-        <v>-5.5691</v>
+        <v>-13.0608</v>
       </c>
       <c r="P16" t="n">
-        <v>8.0085</v>
+        <v>17.249</v>
       </c>
       <c r="Q16" t="n">
-        <v>-12.9365</v>
+        <v>-32.444</v>
       </c>
       <c r="R16" t="n">
-        <v>20.9449</v>
+        <v>49.693</v>
       </c>
       <c r="S16" t="n">
-        <v>-12.1739</v>
+        <v>-1.5864</v>
       </c>
       <c r="T16" t="n">
-        <v>-4.8755</v>
+        <v>-3.8595</v>
       </c>
       <c r="U16" t="n">
-        <v>-7.298299999999999</v>
+        <v>2.2736</v>
       </c>
       <c r="V16" t="n">
-        <v>-5.544</v>
+        <v>8.1259</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4188</v>
+        <v>20.7796</v>
       </c>
       <c r="X16" t="n">
-        <v>-6.962899999999999</v>
+        <v>-12.654</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. CARRASCO MARTIN</t>
+          <t>S. KANE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>-27.1841</v>
+        <v>-19.5318</v>
       </c>
       <c r="E17" t="n">
-        <v>-17.2574</v>
+        <v>-26.7515</v>
       </c>
       <c r="F17" t="n">
-        <v>-9.926500000000001</v>
+        <v>7.2199</v>
       </c>
       <c r="G17" t="n">
-        <v>-6.910099999999999</v>
+        <v>-14.4035</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.729300000000001</v>
+        <v>-13.7548</v>
       </c>
       <c r="I17" t="n">
-        <v>-5.1809</v>
+        <v>-0.6485000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4355</v>
+        <v>-1.511200000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>6.332</v>
+        <v>-5.221</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.8963</v>
+        <v>3.7101</v>
       </c>
       <c r="M17" t="n">
-        <v>-10.3457</v>
+        <v>-12.8923</v>
       </c>
       <c r="N17" t="n">
-        <v>-8.061500000000001</v>
+        <v>-8.533999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.284399999999999</v>
+        <v>-4.3582</v>
       </c>
       <c r="P17" t="n">
-        <v>-13.142</v>
+        <v>-0.6161000000000003</v>
       </c>
       <c r="Q17" t="n">
-        <v>-22.9981</v>
+        <v>-25.4623</v>
       </c>
       <c r="R17" t="n">
-        <v>9.8565</v>
+        <v>24.8462</v>
       </c>
       <c r="S17" t="n">
-        <v>0.05320000000000008</v>
+        <v>4.4225</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4235999999999999</v>
+        <v>2.3803</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4769000000000001</v>
+        <v>2.0424</v>
       </c>
       <c r="V17" t="n">
-        <v>-7.185</v>
+        <v>-8.9352</v>
       </c>
       <c r="W17" t="n">
-        <v>2.7289</v>
+        <v>-2.1584</v>
       </c>
       <c r="X17" t="n">
-        <v>-9.914</v>
+        <v>-6.776800000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X. TORRENT BAYÉ</t>
+          <t>J. CARRASCO MARTIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>-33.4693</v>
+        <v>-27.7198</v>
       </c>
       <c r="E18" t="n">
-        <v>-32.7074</v>
+        <v>-18.745</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7620000000000006</v>
+        <v>-8.974600000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>-40.5118</v>
+        <v>-6.910099999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>-7.8356</v>
+        <v>-1.729300000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-32.6763</v>
+        <v>-5.1809</v>
       </c>
       <c r="J18" t="n">
-        <v>-8.125299999999999</v>
+        <v>3.4355</v>
       </c>
       <c r="K18" t="n">
-        <v>11.4898</v>
+        <v>6.332</v>
       </c>
       <c r="L18" t="n">
-        <v>-19.6153</v>
+        <v>-2.8963</v>
       </c>
       <c r="M18" t="n">
-        <v>-32.3863</v>
+        <v>-10.3457</v>
       </c>
       <c r="N18" t="n">
-        <v>-19.3255</v>
+        <v>-8.061500000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-13.0608</v>
+        <v>-2.284399999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>17.249</v>
+        <v>-13.142</v>
       </c>
       <c r="Q18" t="n">
-        <v>-32.444</v>
+        <v>-22.9981</v>
       </c>
       <c r="R18" t="n">
-        <v>49.693</v>
+        <v>9.8565</v>
       </c>
       <c r="S18" t="n">
-        <v>-18.3321</v>
+        <v>-0.4825000000000002</v>
       </c>
       <c r="T18" t="n">
-        <v>-12.9176</v>
+        <v>-1.9111</v>
       </c>
       <c r="U18" t="n">
-        <v>-5.414400000000001</v>
+        <v>1.4286</v>
       </c>
       <c r="V18" t="n">
-        <v>8.1259</v>
+        <v>-7.185</v>
       </c>
       <c r="W18" t="n">
-        <v>20.7796</v>
+        <v>2.7289</v>
       </c>
       <c r="X18" t="n">
-        <v>-12.654</v>
+        <v>-9.914</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>-36</v>
+        <v>-28.6974</v>
       </c>
       <c r="E19" t="n">
-        <v>-33.3469</v>
+        <v>-27.2488</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.653300000000001</v>
+        <v>-1.448200000000001</v>
       </c>
       <c r="G19" t="n">
         <v>-31.2783</v>
@@ -1936,13 +1936,13 @@
         <v>35.5241</v>
       </c>
       <c r="S19" t="n">
-        <v>-11.5095</v>
+        <v>-4.2066</v>
       </c>
       <c r="T19" t="n">
-        <v>-9.7507</v>
+        <v>-3.6525</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.7588</v>
+        <v>-0.5541</v>
       </c>
       <c r="V19" t="n">
         <v>-9.434200000000001</v>
@@ -1969,13 +1969,13 @@
         <v>14</v>
       </c>
       <c r="D20" t="n">
-        <v>-43.4931</v>
+        <v>-37.2066</v>
       </c>
       <c r="E20" t="n">
-        <v>-28.2531</v>
+        <v>-24.2314</v>
       </c>
       <c r="F20" t="n">
-        <v>-15.2403</v>
+        <v>-12.9751</v>
       </c>
       <c r="G20" t="n">
         <v>-38.4927</v>
@@ -2014,13 +2014,13 @@
         <v>25.0518</v>
       </c>
       <c r="S20" t="n">
-        <v>-12.2835</v>
+        <v>-5.9969</v>
       </c>
       <c r="T20" t="n">
-        <v>-9.2935</v>
+        <v>-5.2722</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.9898</v>
+        <v>-0.7248</v>
       </c>
       <c r="V20" t="n">
         <v>1.327999999999999</v>
@@ -2047,13 +2047,13 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>-106.9158</v>
+        <v>-85.25839999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-120.2694</v>
+        <v>-109.0715</v>
       </c>
       <c r="F21" t="n">
-        <v>13.353</v>
+        <v>23.81429999999999</v>
       </c>
       <c r="G21" t="n">
         <v>-168.686</v>
@@ -2071,7 +2071,7 @@
         <v>114.5203</v>
       </c>
       <c r="L21" t="n">
-        <v>14.42380000000001</v>
+        <v>14.4238</v>
       </c>
       <c r="M21" t="n">
         <v>-297.6307</v>
@@ -2083,7 +2083,7 @@
         <v>-115.0168</v>
       </c>
       <c r="P21" t="n">
-        <v>49.2827</v>
+        <v>49.28270000000001</v>
       </c>
       <c r="Q21" t="n">
         <v>-362.4274</v>
@@ -2092,13 +2092,13 @@
         <v>411.7107</v>
       </c>
       <c r="S21" t="n">
-        <v>-14.1442</v>
+        <v>7.5144</v>
       </c>
       <c r="T21" t="n">
-        <v>-33.3982</v>
+        <v>-22.1995</v>
       </c>
       <c r="U21" t="n">
-        <v>19.2545</v>
+        <v>29.71430000000001</v>
       </c>
       <c r="V21" t="n">
         <v>26.632</v>
